--- a/Assignment-brief.xlsx
+++ b/Assignment-brief.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Data analytics\Sales-Operations-Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B7BDA7-E788-4102-8C01-B3C436D0F08B}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F549E0-DAC3-46C8-8584-8DBC9E45DE21}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Brief" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>15) Ensure your dashboard responds to slicers without broken references.</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>IF(Dis&gt;0.2,"Non-Compliant","Compliant")</t>
+  </si>
+  <si>
+    <t>Not Yet</t>
   </si>
 </sst>
 </file>
@@ -246,7 +249,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,6 +292,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -317,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -342,6 +351,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,96 +862,99 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>3</v>
       </c>
